--- a/MIS-crm-lead-analysis.xlsx
+++ b/MIS-crm-lead-analysis.xlsx
@@ -2,21 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tech\Projects\Excel\crm lead analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AFDAA4-FC64-46C1-A0DA-4DBC7673AE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2600DA57-AC6F-419D-A2CD-6C02CFB87496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw CRM Dump" sheetId="2" r:id="rId1"/>
     <sheet name="Cleaned Data" sheetId="13" r:id="rId2"/>
     <sheet name="Summary" sheetId="11" r:id="rId3"/>
-    <sheet name="Dashboard &amp; Pivot table" sheetId="14" r:id="rId4"/>
+    <sheet name="Pivot" sheetId="15" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="14" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cleaned Data'!$A$1:$J$1</definedName>
@@ -25,13 +26,13 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="7" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId6"/>
         <x14:slicerCache r:id="rId7"/>
+        <x14:slicerCache r:id="rId8"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8885" uniqueCount="1624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8972" uniqueCount="1628">
   <si>
     <t>Lead ID</t>
   </si>
@@ -4931,13 +4932,25 @@
   </si>
   <si>
     <t xml:space="preserve">          Total Leads</t>
+  </si>
+  <si>
+    <t>Lead Source Vs City</t>
+  </si>
+  <si>
+    <t>Essential Pivot Summary</t>
+  </si>
+  <si>
+    <t>Lead Source Count</t>
+  </si>
+  <si>
+    <t>Status vs Lead Source</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="43" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5222,8 +5235,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5380,6 +5416,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5613,7 +5661,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5878,6 +5926,35 @@
     <xf numFmtId="0" fontId="41" fillId="26" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="22" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5914,35 +5991,6 @@
     <xf numFmtId="0" fontId="33" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5967,12 +6015,144 @@
     <xf numFmtId="0" fontId="42" fillId="27" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="13" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="13" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FDF0028C-19FC-4E27-AC2A-BC00617EBE48}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="20">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6084,7 +6264,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[MIS_Assignment_tbs.xlsx]Dashboard &amp; Pivot table!PivotTable1</c:name>
+    <c:name>[MIS-crm-lead-analysis.xlsx]Dashboard!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -6169,6 +6349,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -6208,6 +6389,19 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:view3D>
@@ -6260,7 +6454,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$Z$5</c:f>
+              <c:f>Dashboard!$Z$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6281,6 +6475,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -6339,7 +6534,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$Y$6:$Y$13</c:f>
+              <c:f>Dashboard!$Y$6:$Y$13</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
@@ -6368,7 +6563,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard &amp; Pivot table'!$Z$6:$Z$13</c:f>
+              <c:f>Dashboard!$Z$6:$Z$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -6420,6 +6615,63 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Source</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -6479,6 +6731,63 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Total</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -6528,7 +6837,9 @@
       <c:spPr>
         <a:noFill/>
         <a:ln>
-          <a:noFill/>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -6537,7 +6848,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -6570,10 +6881,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="tx1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -6627,7 +6935,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[MIS_Assignment_tbs.xlsx]Dashboard &amp; Pivot table!PivotTable4</c:name>
+    <c:name>[MIS-crm-lead-analysis.xlsx]Dashboard!PivotTable4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -6710,7 +7018,9 @@
           <c:spPr>
             <a:noFill/>
             <a:ln>
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -6721,7 +7031,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -6798,7 +7108,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AI$5</c:f>
+              <c:f>Dashboard!$AI$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6822,7 +7132,9 @@
             <c:spPr>
               <a:noFill/>
               <a:ln>
-                <a:noFill/>
+                <a:solidFill>
+                  <a:schemeClr val="bg2"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -6833,7 +7145,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -6877,7 +7189,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AH$6:$AH$15</c:f>
+              <c:f>Dashboard!$AH$6:$AH$15</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -6912,7 +7224,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AI$6:$AI$15</c:f>
+              <c:f>Dashboard!$AI$6:$AI$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -6974,11 +7286,38 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>CIty</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -7063,11 +7402,38 @@
           </c:spPr>
         </c:majorGridlines>
         <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>Total</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -7152,10 +7518,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="tx1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -7208,7 +7571,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[MIS_Assignment_tbs.xlsx]Dashboard &amp; Pivot table!PivotTable3</c:name>
+    <c:name>[MIS-crm-lead-analysis.xlsx]Dashboard!PivotTable3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -7259,40 +7622,46 @@
         <c:dLbl>
           <c:idx val="0"/>
           <c:spPr>
-            <a:noFill/>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
             <a:ln>
-              <a:noFill/>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="accent1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
+                <a:defRPr/>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
           <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="1"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+              </c15:spPr>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -7321,6 +7690,57 @@
             <a:bevelB w="127000" h="127000"/>
           </a:sp3d>
         </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0.13125559903814418"/>
+              <c:y val="1.4153774119943511E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
@@ -7373,6 +7793,57 @@
             <a:bevelB w="127000" h="127000"/>
           </a:sp3d>
         </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+              </c15:spPr>
+              <c15:layout>
+                <c:manualLayout>
+                  <c:w val="5.3416094575921745E-2"/>
+                  <c:h val="8.5498790673143865E-2"/>
+                </c:manualLayout>
+              </c15:layout>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="4"/>
@@ -7425,6 +7896,63 @@
             <a:bevelB w="127000" h="127000"/>
           </a:sp3d>
         </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="-4.8746518105849582E-2"/>
+              <c:y val="-3.4013605442176881E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+              </c15:spPr>
+              <c15:layout>
+                <c:manualLayout>
+                  <c:w val="7.0225083285202161E-2"/>
+                  <c:h val="9.3348084236723139E-2"/>
+                </c:manualLayout>
+              </c15:layout>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:view3D>
@@ -7485,7 +8013,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AD$5</c:f>
+              <c:f>Dashboard!$AD$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7655,61 +8183,189 @@
             </c:extLst>
           </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.13125559903814418"/>
+                  <c:y val="1.4153774119943511E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-9F03-4222-92B6-C308AB5243EB}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:noAutofit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                  </c15:spPr>
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="5.3416094575921745E-2"/>
+                      <c:h val="8.5498790673143865E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-9F03-4222-92B6-C308AB5243EB}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.8746518105849582E-2"/>
+                  <c:y val="-3.4013605442176881E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:noAutofit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                  </c15:spPr>
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="7.0225083285202161E-2"/>
+                      <c:h val="9.3348084236723139E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-9F03-4222-92B6-C308AB5243EB}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
-              <a:noFill/>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
               <a:ln>
-                <a:noFill/>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="accent1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="1"/>
             <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
+            <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="35000"/>
-                      <a:lumOff val="65000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                </c15:spPr>
+              </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AC$6:$AC$11</c:f>
+              <c:f>Dashboard!$AC$6:$AC$11</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -7732,7 +8388,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AD$6:$AD$11</c:f>
+              <c:f>Dashboard!$AD$6:$AD$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -7768,7 +8424,7 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
+          <c:showLeaderLines val="0"/>
         </c:dLbls>
       </c:pie3DChart>
       <c:spPr>
@@ -7796,10 +8452,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="tx1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -7925,7 +8578,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AI$19</c:f>
+              <c:f>Dashboard!$AI$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8006,7 +8659,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AH$20:$AH$22</c:f>
+              <c:f>Dashboard!$AH$20:$AH$22</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -8023,7 +8676,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AI$20:$AI$22</c:f>
+              <c:f>Dashboard!$AI$20:$AI$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -8051,7 +8704,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AJ$19</c:f>
+              <c:f>Dashboard!$AJ$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8132,7 +8785,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AH$20:$AH$22</c:f>
+              <c:f>Dashboard!$AH$20:$AH$22</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -8149,7 +8802,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard &amp; Pivot table'!$AJ$20:$AJ$22</c:f>
+              <c:f>Dashboard!$AJ$20:$AJ$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -8277,15 +8930,15 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-IN"/>
+                  <a:rPr lang="en-IN" b="1"/>
                   <a:t> Total</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-IN" baseline="0"/>
+                  <a:rPr lang="en-IN" b="1" baseline="0"/>
                   <a:t> </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-IN"/>
+                  <a:rPr lang="en-IN" b="1"/>
                   <a:t>Leads</a:t>
                 </a:r>
               </a:p>
@@ -8295,7 +8948,9 @@
           <c:spPr>
             <a:noFill/>
             <a:ln>
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -8411,10 +9066,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="tx1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -10223,15 +10875,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>437520</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>136800</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10259,15 +10911,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
+      <xdr:colOff>9207</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>49530</xdr:rowOff>
+      <xdr:rowOff>29528</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>224160</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>3450</xdr:rowOff>
+      <xdr:colOff>246063</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10295,15 +10947,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>201300</xdr:colOff>
+      <xdr:colOff>213360</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>136800</xdr:rowOff>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10331,15 +10983,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>281940</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>174624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>445140</xdr:colOff>
+      <xdr:colOff>468313</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>174900</xdr:rowOff>
+      <xdr:rowOff>134937</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -16788,7 +17440,883 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31E788D7-40A0-40B2-A317-DA6B0660CE70}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21B24398-9E80-4734-B61C-24441E54D88B}" name="PivotTable5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Lead Source" colHeaderCaption="Lead Source">
+  <location ref="K29:L37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="3"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="3">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAAA9618-C1D4-45B1-956F-7CC2F0CD5445}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status" colHeaderCaption="Lead Source">
+  <location ref="K18:L24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="3"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="9">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F3B9D49-92D9-4566-BE5D-DD2A5860D248}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="Lead Source">
+  <location ref="K3:Q14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="3"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Lead Source Vs City" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="11">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2C4BD05D-53FE-452F-AB86-9DF35BCA8C1A}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="Lead Source">
+  <location ref="A21:I35" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="3"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="12">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2AE6040-D966-432E-93ED-5335F72967F7}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="Status">
+  <location ref="A3:G17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="3"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Status" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="13">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4D65842-9FA9-40F1-AAF3-FCF35EBE950A}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="Y5:Z13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{602D481F-4888-46B5-972C-75DBB87DFC26}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="AH5:AI15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="10">
+        <item x="8"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31E788D7-40A0-40B2-A317-DA6B0660CE70}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="Y18:AE32" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -16922,8 +18450,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63F87A7D-152C-4B09-B0D3-6D55A408A4DF}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63F87A7D-152C-4B09-B0D3-6D55A408A4DF}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="AC5:AD11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -17071,222 +18599,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4D65842-9FA9-40F1-AAF3-FCF35EBE950A}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="Y5:Z13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{602D481F-4888-46B5-972C-75DBB87DFC26}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="AH5:AI15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="10">
-        <item x="8"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Status" xr10:uid="{00B61D08-ABD8-4045-9401-657E2FA74DAB}" sourceName="Status">
   <pivotTables>
@@ -17343,7 +18655,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C87595D-82F3-446B-89E4-6167E343AA19}" name="Table1" displayName="Table1" ref="A1:J501" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C87595D-82F3-446B-89E4-6167E343AA19}" name="Table1" displayName="Table1" ref="A1:J501" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J501" xr:uid="{5C87595D-82F3-446B-89E4-6167E343AA19}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{C149B129-AE4D-4DD0-9641-07FBD4EF87BF}" name="Lead ID"/>
@@ -17351,7 +18663,7 @@
     <tableColumn id="3" xr3:uid="{7BA7FB96-DB65-4C8A-9A25-A8B41149054F}" name="Lead Source"/>
     <tableColumn id="4" xr3:uid="{D87AA976-B442-495C-9B6E-47BB706054D2}" name="Phone Number"/>
     <tableColumn id="5" xr3:uid="{48408B5D-907C-4098-B88B-B0DE9A939C87}" name="Email"/>
-    <tableColumn id="6" xr3:uid="{19C4F1A2-FDBC-4D39-BC2C-D2BFEA358B52}" name="Lead Date" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{19C4F1A2-FDBC-4D39-BC2C-D2BFEA358B52}" name="Lead Date" dataDxfId="15"/>
     <tableColumn id="7" xr3:uid="{56DF7A39-C11C-437F-A0C4-26D6F908230B}" name="Status"/>
     <tableColumn id="8" xr3:uid="{EC0B42EF-22F9-4263-9D97-6A3F3FDD463C}" name="City"/>
     <tableColumn id="9" xr3:uid="{AF14FE2D-0051-4A82-A5FB-0EEEB0A87D7A}" name="Follow-up Done"/>
@@ -47859,34 +49171,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="120" t="s">
         <v>1506</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
       <c r="L1"/>
       <c r="M1"/>
     </row>
     <row r="2" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="121" t="s">
         <v>1505</v>
       </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
       <c r="L2"/>
       <c r="M2"/>
     </row>
@@ -47895,83 +49207,83 @@
       <c r="M3"/>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="109" t="s">
+      <c r="A4" s="122" t="s">
         <v>1504</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="110" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="123" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="111" t="s">
+      <c r="D4" s="123"/>
+      <c r="E4" s="124" t="s">
         <v>1503</v>
       </c>
-      <c r="F4" s="111"/>
-      <c r="G4" s="112" t="s">
+      <c r="F4" s="124"/>
+      <c r="G4" s="125" t="s">
         <v>1502</v>
       </c>
-      <c r="H4" s="112"/>
-      <c r="I4" s="113" t="s">
+      <c r="H4" s="125"/>
+      <c r="I4" s="126" t="s">
         <v>1501</v>
       </c>
-      <c r="J4" s="113"/>
+      <c r="J4" s="126"/>
       <c r="L4"/>
       <c r="M4"/>
     </row>
     <row r="5" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="104">
+      <c r="A5" s="117">
         <f>COUNTA('Cleaned Data'!G2:G501)</f>
         <v>500</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="105">
+      <c r="B5" s="117"/>
+      <c r="C5" s="118">
         <f>COUNTIF('Cleaned Data'!G1:G505,"Converted")</f>
         <v>184</v>
       </c>
-      <c r="D5" s="106"/>
-      <c r="E5" s="114">
+      <c r="D5" s="119"/>
+      <c r="E5" s="127">
         <f>C5/A5</f>
         <v>0.36799999999999999</v>
       </c>
-      <c r="F5" s="114"/>
-      <c r="G5" s="115">
+      <c r="F5" s="127"/>
+      <c r="G5" s="128">
         <f>COUNTIFS('Cleaned Data'!G1:G501,"Callback")+COUNTIFS('Cleaned Data'!G1:G501,"Open")</f>
         <v>195</v>
       </c>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115">
+      <c r="H5" s="128"/>
+      <c r="I5" s="128">
         <f>COUNTIFS('Cleaned Data'!G1:G501,"Lost")+COUNTIFS('Cleaned Data'!G1:G501,"Not interested")</f>
         <v>121</v>
       </c>
-      <c r="J5" s="115"/>
+      <c r="J5" s="128"/>
       <c r="L5"/>
       <c r="M5"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="120"/>
-      <c r="B6" s="120"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="123"/>
-      <c r="J6" s="123"/>
+      <c r="A6" s="108"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
       <c r="L6"/>
       <c r="M6"/>
     </row>
     <row r="7" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="120"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="123"/>
-      <c r="J7" s="123"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
       <c r="L7"/>
       <c r="M7"/>
     </row>
@@ -47980,19 +49292,19 @@
       <c r="M8"/>
     </row>
     <row r="9" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="117" t="s">
+      <c r="A9" s="105" t="s">
         <v>1500</v>
       </c>
-      <c r="B9" s="117"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="124" t="s">
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="112" t="s">
         <v>1499</v>
       </c>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="126"/>
+      <c r="G9" s="113"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="114"/>
       <c r="J9"/>
       <c r="L9"/>
       <c r="M9"/>
@@ -48274,17 +49586,17 @@
     </row>
     <row r="19" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="117" t="s">
+      <c r="A20" s="105" t="s">
         <v>1488</v>
       </c>
-      <c r="B20" s="127"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="128"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="116"/>
       <c r="J20"/>
     </row>
     <row r="21" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -48713,57 +50025,90 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="138" t="s">
         <v>153</v>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="139">
         <f>COUNTIF('Cleaned Data'!$B$2:$B$501,A33)</f>
         <v>6</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="139">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!C$21)</f>
         <v>3</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="139">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!D$21)</f>
         <v>2</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="139">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!E$21)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="139">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!F$21)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="26">
+      <c r="G33" s="139">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!G$21)</f>
         <v>1</v>
       </c>
-      <c r="H33" s="68">
+      <c r="H33" s="140">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="141" t="s">
         <v>1475</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="142" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B34" s="143">
+        <f>SUM(B22:B33)</f>
+        <v>500</v>
+      </c>
+      <c r="C34" s="143">
+        <f t="shared" ref="C34:G34" si="3">SUM(C22:C33)</f>
+        <v>184</v>
+      </c>
+      <c r="D34" s="143">
+        <f t="shared" si="3"/>
+        <v>134</v>
+      </c>
+      <c r="E34" s="143">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="F34" s="143">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="G34" s="144">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="H34" s="146"/>
+      <c r="I34" s="145"/>
+    </row>
+    <row r="35" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="137"/>
+    </row>
     <row r="36" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="118" t="s">
+      <c r="A36" s="106" t="s">
         <v>1474</v>
       </c>
-      <c r="B36" s="118"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="119" t="s">
+      <c r="B36" s="106"/>
+      <c r="C36" s="106"/>
+      <c r="D36" s="106"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="107" t="s">
         <v>1473</v>
       </c>
-      <c r="G36" s="119"/>
-      <c r="H36" s="119"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="119"/>
+      <c r="G36" s="107"/>
+      <c r="H36" s="107"/>
+      <c r="I36" s="107"/>
+      <c r="J36" s="107"/>
     </row>
     <row r="37" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
@@ -48838,7 +50183,7 @@
         <v>64</v>
       </c>
       <c r="C39" s="69">
-        <f t="shared" ref="C39:C46" si="3">$B39/500</f>
+        <f t="shared" ref="C39:C46" si="4">$B39/500</f>
         <v>0.128</v>
       </c>
       <c r="D39" s="20" t="s">
@@ -48872,7 +50217,7 @@
         <v>61</v>
       </c>
       <c r="C40" s="69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.122</v>
       </c>
       <c r="D40" s="19" t="s">
@@ -48906,7 +50251,7 @@
         <v>56</v>
       </c>
       <c r="C41" s="69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.112</v>
       </c>
       <c r="D41" s="16" t="s">
@@ -48925,7 +50270,7 @@
         <v>55</v>
       </c>
       <c r="C42" s="69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.11</v>
       </c>
       <c r="D42" s="15" t="s">
@@ -48944,7 +50289,7 @@
         <v>53</v>
       </c>
       <c r="C43" s="69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.106</v>
       </c>
       <c r="D43" s="14" t="s">
@@ -48963,7 +50308,7 @@
         <v>52</v>
       </c>
       <c r="C44" s="69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.104</v>
       </c>
       <c r="D44" s="11" t="s">
@@ -48982,7 +50327,7 @@
         <v>45</v>
       </c>
       <c r="C45" s="69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.09</v>
       </c>
       <c r="D45" s="7" t="s">
@@ -49001,12 +50346,24 @@
         <v>44</v>
       </c>
       <c r="C46" s="69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A36:E36"/>
@@ -49022,26 +50379,14 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <conditionalFormatting sqref="D11:D15">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="14" priority="5">
       <formula>$C$11&gt;30</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J17">
-    <cfRule type="iconSet" priority="2">
+    <cfRule type="iconSet" priority="3">
       <iconSet iconSet="3TrafficLights2">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
@@ -49050,6 +50395,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H33">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -49067,7 +50424,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{66A0FF2D-E75F-4538-8026-0166FC16A52C}">
+          <x14:cfRule type="iconSet" priority="4" id="{66A0FF2D-E75F-4538-8026-0166FC16A52C}">
             <x14:iconSet iconSet="3Stars" showValue="0">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -49089,6 +50446,1109 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69513737-AD63-44D1-8F5C-9E1B869F8EE0}">
+  <dimension ref="A1:Q37"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="149" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="149"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="147" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B3" s="89" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="147" t="s">
+        <v>1624</v>
+      </c>
+      <c r="L3" s="89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="89" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B4" s="148" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="63" t="s">
+        <v>1614</v>
+      </c>
+      <c r="K4" s="89" t="s">
+        <v>1613</v>
+      </c>
+      <c r="L4" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="M4" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="O4" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4" s="63" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="90" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="91">
+        <v>1</v>
+      </c>
+      <c r="C5" s="91">
+        <v>7</v>
+      </c>
+      <c r="D5" s="91">
+        <v>2</v>
+      </c>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91">
+        <v>5</v>
+      </c>
+      <c r="G5" s="91">
+        <v>15</v>
+      </c>
+      <c r="K5" s="90" t="s">
+        <v>125</v>
+      </c>
+      <c r="L5" s="91">
+        <v>9</v>
+      </c>
+      <c r="M5" s="91">
+        <v>19</v>
+      </c>
+      <c r="N5" s="91">
+        <v>4</v>
+      </c>
+      <c r="O5" s="91">
+        <v>7</v>
+      </c>
+      <c r="P5" s="91">
+        <v>16</v>
+      </c>
+      <c r="Q5" s="91">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="90" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="91">
+        <v>1</v>
+      </c>
+      <c r="C6" s="91">
+        <v>5</v>
+      </c>
+      <c r="D6" s="91"/>
+      <c r="E6" s="91">
+        <v>2</v>
+      </c>
+      <c r="F6" s="91">
+        <v>2</v>
+      </c>
+      <c r="G6" s="91">
+        <v>10</v>
+      </c>
+      <c r="K6" s="90" t="s">
+        <v>1619</v>
+      </c>
+      <c r="L6" s="91">
+        <v>8</v>
+      </c>
+      <c r="M6" s="91">
+        <v>18</v>
+      </c>
+      <c r="N6" s="91">
+        <v>6</v>
+      </c>
+      <c r="O6" s="91">
+        <v>3</v>
+      </c>
+      <c r="P6" s="91">
+        <v>9</v>
+      </c>
+      <c r="Q6" s="91">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="90" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="91">
+        <v>6</v>
+      </c>
+      <c r="C7" s="91">
+        <v>17</v>
+      </c>
+      <c r="D7" s="91">
+        <v>9</v>
+      </c>
+      <c r="E7" s="91">
+        <v>3</v>
+      </c>
+      <c r="F7" s="91">
+        <v>16</v>
+      </c>
+      <c r="G7" s="91">
+        <v>51</v>
+      </c>
+      <c r="K7" s="90" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="91">
+        <v>4</v>
+      </c>
+      <c r="M7" s="91">
+        <v>22</v>
+      </c>
+      <c r="N7" s="91">
+        <v>3</v>
+      </c>
+      <c r="O7" s="91">
+        <v>5</v>
+      </c>
+      <c r="P7" s="91">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="91">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="90" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="91">
+        <v>5</v>
+      </c>
+      <c r="C8" s="91">
+        <v>12</v>
+      </c>
+      <c r="D8" s="91">
+        <v>8</v>
+      </c>
+      <c r="E8" s="91">
+        <v>4</v>
+      </c>
+      <c r="F8" s="91">
+        <v>15</v>
+      </c>
+      <c r="G8" s="91">
+        <v>44</v>
+      </c>
+      <c r="K8" s="90" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="91">
+        <v>6</v>
+      </c>
+      <c r="M8" s="91">
+        <v>28</v>
+      </c>
+      <c r="N8" s="91">
+        <v>8</v>
+      </c>
+      <c r="O8" s="91">
+        <v>10</v>
+      </c>
+      <c r="P8" s="91">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="91">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="90" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="91">
+        <v>7</v>
+      </c>
+      <c r="C9" s="91">
+        <v>21</v>
+      </c>
+      <c r="D9" s="91">
+        <v>6</v>
+      </c>
+      <c r="E9" s="91">
+        <v>9</v>
+      </c>
+      <c r="F9" s="91">
+        <v>22</v>
+      </c>
+      <c r="G9" s="91">
+        <v>65</v>
+      </c>
+      <c r="K9" s="90" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="91">
+        <v>11</v>
+      </c>
+      <c r="M9" s="91">
+        <v>14</v>
+      </c>
+      <c r="N9" s="91">
+        <v>6</v>
+      </c>
+      <c r="O9" s="91">
+        <v>6</v>
+      </c>
+      <c r="P9" s="91">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="91">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="90" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" s="91">
+        <v>9</v>
+      </c>
+      <c r="C10" s="91">
+        <v>25</v>
+      </c>
+      <c r="D10" s="91">
+        <v>8</v>
+      </c>
+      <c r="E10" s="91">
+        <v>6</v>
+      </c>
+      <c r="F10" s="91">
+        <v>12</v>
+      </c>
+      <c r="G10" s="91">
+        <v>60</v>
+      </c>
+      <c r="K10" s="90" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" s="91">
+        <v>3</v>
+      </c>
+      <c r="M10" s="91">
+        <v>25</v>
+      </c>
+      <c r="N10" s="91">
+        <v>10</v>
+      </c>
+      <c r="O10" s="91">
+        <v>9</v>
+      </c>
+      <c r="P10" s="91">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="91">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="90" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="91">
+        <v>7</v>
+      </c>
+      <c r="C11" s="91">
+        <v>30</v>
+      </c>
+      <c r="D11" s="91">
+        <v>8</v>
+      </c>
+      <c r="E11" s="91">
+        <v>9</v>
+      </c>
+      <c r="F11" s="91">
+        <v>18</v>
+      </c>
+      <c r="G11" s="91">
+        <v>72</v>
+      </c>
+      <c r="K11" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="91">
+        <v>4</v>
+      </c>
+      <c r="M11" s="91">
+        <v>16</v>
+      </c>
+      <c r="N11" s="91">
+        <v>12</v>
+      </c>
+      <c r="O11" s="91">
+        <v>6</v>
+      </c>
+      <c r="P11" s="91">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="91">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="90" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91">
+        <v>3</v>
+      </c>
+      <c r="D12" s="91">
+        <v>1</v>
+      </c>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91">
+        <v>2</v>
+      </c>
+      <c r="G12" s="91">
+        <v>6</v>
+      </c>
+      <c r="K12" s="90" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="91">
+        <v>9</v>
+      </c>
+      <c r="M12" s="91">
+        <v>16</v>
+      </c>
+      <c r="N12" s="91">
+        <v>5</v>
+      </c>
+      <c r="O12" s="91">
+        <v>5</v>
+      </c>
+      <c r="P12" s="91">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="91">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="90" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="91">
+        <v>4</v>
+      </c>
+      <c r="C13" s="91">
+        <v>10</v>
+      </c>
+      <c r="D13" s="91">
+        <v>1</v>
+      </c>
+      <c r="E13" s="91">
+        <v>1</v>
+      </c>
+      <c r="F13" s="91">
+        <v>2</v>
+      </c>
+      <c r="G13" s="91">
+        <v>18</v>
+      </c>
+      <c r="K13" s="90" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="91">
+        <v>7</v>
+      </c>
+      <c r="M13" s="91">
+        <v>26</v>
+      </c>
+      <c r="N13" s="91">
+        <v>6</v>
+      </c>
+      <c r="O13" s="91">
+        <v>10</v>
+      </c>
+      <c r="P13" s="91">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="90" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="91">
+        <v>7</v>
+      </c>
+      <c r="C14" s="91">
+        <v>15</v>
+      </c>
+      <c r="D14" s="91">
+        <v>5</v>
+      </c>
+      <c r="E14" s="91">
+        <v>8</v>
+      </c>
+      <c r="F14" s="91">
+        <v>11</v>
+      </c>
+      <c r="G14" s="91">
+        <v>46</v>
+      </c>
+      <c r="K14" s="90" t="s">
+        <v>1614</v>
+      </c>
+      <c r="L14" s="91">
+        <v>61</v>
+      </c>
+      <c r="M14" s="91">
+        <v>184</v>
+      </c>
+      <c r="N14" s="91">
+        <v>60</v>
+      </c>
+      <c r="O14" s="91">
+        <v>61</v>
+      </c>
+      <c r="P14" s="91">
+        <v>134</v>
+      </c>
+      <c r="Q14" s="91">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="90" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="91">
+        <v>8</v>
+      </c>
+      <c r="C15" s="91">
+        <v>16</v>
+      </c>
+      <c r="D15" s="91">
+        <v>4</v>
+      </c>
+      <c r="E15" s="91">
+        <v>9</v>
+      </c>
+      <c r="F15" s="91">
+        <v>14</v>
+      </c>
+      <c r="G15" s="91">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="90" t="s">
+        <v>597</v>
+      </c>
+      <c r="B16" s="91">
+        <v>6</v>
+      </c>
+      <c r="C16" s="91">
+        <v>23</v>
+      </c>
+      <c r="D16" s="91">
+        <v>8</v>
+      </c>
+      <c r="E16" s="91">
+        <v>10</v>
+      </c>
+      <c r="F16" s="91">
+        <v>15</v>
+      </c>
+      <c r="G16" s="91">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="90" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B17" s="91">
+        <v>61</v>
+      </c>
+      <c r="C17" s="91">
+        <v>184</v>
+      </c>
+      <c r="D17" s="91">
+        <v>60</v>
+      </c>
+      <c r="E17" s="91">
+        <v>61</v>
+      </c>
+      <c r="F17" s="91">
+        <v>134</v>
+      </c>
+      <c r="G17" s="91">
+        <v>500</v>
+      </c>
+      <c r="K17" s="150" t="s">
+        <v>1627</v>
+      </c>
+      <c r="L17" s="150"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K18" s="89" t="s">
+        <v>6</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K19" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="L19" s="91">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K20" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="91">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="147" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B21" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="K21" s="90" t="s">
+        <v>111</v>
+      </c>
+      <c r="L21" s="91">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="89" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="63" t="s">
+        <v>1617</v>
+      </c>
+      <c r="I22" s="63" t="s">
+        <v>1614</v>
+      </c>
+      <c r="K22" s="90" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="91">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="90" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="91">
+        <v>3</v>
+      </c>
+      <c r="C23" s="91">
+        <v>3</v>
+      </c>
+      <c r="D23" s="91">
+        <v>1</v>
+      </c>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91">
+        <v>3</v>
+      </c>
+      <c r="G23" s="91">
+        <v>2</v>
+      </c>
+      <c r="H23" s="91"/>
+      <c r="I23" s="91">
+        <v>12</v>
+      </c>
+      <c r="K23" s="90" t="s">
+        <v>79</v>
+      </c>
+      <c r="L23" s="91">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="90" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="91">
+        <v>1</v>
+      </c>
+      <c r="C24" s="91">
+        <v>4</v>
+      </c>
+      <c r="D24" s="91">
+        <v>1</v>
+      </c>
+      <c r="E24" s="91"/>
+      <c r="F24" s="91">
+        <v>1</v>
+      </c>
+      <c r="G24" s="91">
+        <v>3</v>
+      </c>
+      <c r="H24" s="91"/>
+      <c r="I24" s="91">
+        <v>10</v>
+      </c>
+      <c r="K24" s="90" t="s">
+        <v>1614</v>
+      </c>
+      <c r="L24" s="91">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="90" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="91">
+        <v>6</v>
+      </c>
+      <c r="C25" s="91">
+        <v>4</v>
+      </c>
+      <c r="D25" s="91">
+        <v>6</v>
+      </c>
+      <c r="E25" s="91">
+        <v>6</v>
+      </c>
+      <c r="F25" s="91">
+        <v>8</v>
+      </c>
+      <c r="G25" s="91">
+        <v>9</v>
+      </c>
+      <c r="H25" s="91"/>
+      <c r="I25" s="91">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="90" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="91">
+        <v>11</v>
+      </c>
+      <c r="C26" s="91">
+        <v>7</v>
+      </c>
+      <c r="D26" s="91">
+        <v>3</v>
+      </c>
+      <c r="E26" s="91">
+        <v>6</v>
+      </c>
+      <c r="F26" s="91">
+        <v>3</v>
+      </c>
+      <c r="G26" s="91">
+        <v>8</v>
+      </c>
+      <c r="H26" s="91"/>
+      <c r="I26" s="91">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="90" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="91">
+        <v>8</v>
+      </c>
+      <c r="C27" s="91">
+        <v>7</v>
+      </c>
+      <c r="D27" s="91">
+        <v>9</v>
+      </c>
+      <c r="E27" s="91">
+        <v>6</v>
+      </c>
+      <c r="F27" s="91">
+        <v>8</v>
+      </c>
+      <c r="G27" s="91">
+        <v>13</v>
+      </c>
+      <c r="H27" s="91"/>
+      <c r="I27" s="91">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="90" t="s">
+        <v>227</v>
+      </c>
+      <c r="B28" s="91">
+        <v>7</v>
+      </c>
+      <c r="C28" s="91">
+        <v>5</v>
+      </c>
+      <c r="D28" s="91">
+        <v>10</v>
+      </c>
+      <c r="E28" s="91">
+        <v>5</v>
+      </c>
+      <c r="F28" s="91">
+        <v>9</v>
+      </c>
+      <c r="G28" s="91">
+        <v>8</v>
+      </c>
+      <c r="H28" s="91"/>
+      <c r="I28" s="91">
+        <v>44</v>
+      </c>
+      <c r="K28" s="150" t="s">
+        <v>1626</v>
+      </c>
+      <c r="L28" s="150"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="90" t="s">
+        <v>202</v>
+      </c>
+      <c r="B29" s="91">
+        <v>9</v>
+      </c>
+      <c r="C29" s="91">
+        <v>12</v>
+      </c>
+      <c r="D29" s="91">
+        <v>11</v>
+      </c>
+      <c r="E29" s="91">
+        <v>8</v>
+      </c>
+      <c r="F29" s="91">
+        <v>12</v>
+      </c>
+      <c r="G29" s="91">
+        <v>11</v>
+      </c>
+      <c r="H29" s="91"/>
+      <c r="I29" s="91">
+        <v>63</v>
+      </c>
+      <c r="K29" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="L29" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="90" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="91">
+        <v>1</v>
+      </c>
+      <c r="C30" s="91">
+        <v>1</v>
+      </c>
+      <c r="D30" s="91"/>
+      <c r="E30" s="91">
+        <v>1</v>
+      </c>
+      <c r="F30" s="91">
+        <v>2</v>
+      </c>
+      <c r="G30" s="91">
+        <v>1</v>
+      </c>
+      <c r="H30" s="91"/>
+      <c r="I30" s="91">
+        <v>6</v>
+      </c>
+      <c r="K30" s="90" t="s">
+        <v>37</v>
+      </c>
+      <c r="L30" s="91">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="90" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="91">
+        <v>4</v>
+      </c>
+      <c r="C31" s="91">
+        <v>2</v>
+      </c>
+      <c r="D31" s="91">
+        <v>3</v>
+      </c>
+      <c r="E31" s="91">
+        <v>5</v>
+      </c>
+      <c r="F31" s="91">
+        <v>3</v>
+      </c>
+      <c r="G31" s="91">
+        <v>1</v>
+      </c>
+      <c r="H31" s="91"/>
+      <c r="I31" s="91">
+        <v>18</v>
+      </c>
+      <c r="K31" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="L31" s="91">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="90" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="91">
+        <v>7</v>
+      </c>
+      <c r="C32" s="91">
+        <v>5</v>
+      </c>
+      <c r="D32" s="91">
+        <v>8</v>
+      </c>
+      <c r="E32" s="91">
+        <v>3</v>
+      </c>
+      <c r="F32" s="91">
+        <v>7</v>
+      </c>
+      <c r="G32" s="91">
+        <v>5</v>
+      </c>
+      <c r="H32" s="91"/>
+      <c r="I32" s="91">
+        <v>35</v>
+      </c>
+      <c r="K32" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="L32" s="91">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="90" t="s">
+        <v>206</v>
+      </c>
+      <c r="B33" s="91">
+        <v>13</v>
+      </c>
+      <c r="C33" s="91">
+        <v>4</v>
+      </c>
+      <c r="D33" s="91">
+        <v>2</v>
+      </c>
+      <c r="E33" s="91">
+        <v>10</v>
+      </c>
+      <c r="F33" s="91">
+        <v>6</v>
+      </c>
+      <c r="G33" s="91">
+        <v>6</v>
+      </c>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91">
+        <v>41</v>
+      </c>
+      <c r="K33" s="90" t="s">
+        <v>119</v>
+      </c>
+      <c r="L33" s="91">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="90" t="s">
+        <v>597</v>
+      </c>
+      <c r="B34" s="91">
+        <v>1</v>
+      </c>
+      <c r="C34" s="91">
+        <v>1</v>
+      </c>
+      <c r="D34" s="91">
+        <v>10</v>
+      </c>
+      <c r="E34" s="91">
+        <v>12</v>
+      </c>
+      <c r="F34" s="91">
+        <v>11</v>
+      </c>
+      <c r="G34" s="91">
+        <v>8</v>
+      </c>
+      <c r="H34" s="91"/>
+      <c r="I34" s="91">
+        <v>43</v>
+      </c>
+      <c r="K34" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="91">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="90" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B35" s="91">
+        <v>71</v>
+      </c>
+      <c r="C35" s="91">
+        <v>55</v>
+      </c>
+      <c r="D35" s="91">
+        <v>64</v>
+      </c>
+      <c r="E35" s="91">
+        <v>62</v>
+      </c>
+      <c r="F35" s="91">
+        <v>73</v>
+      </c>
+      <c r="G35" s="91">
+        <v>75</v>
+      </c>
+      <c r="H35" s="91"/>
+      <c r="I35" s="91">
+        <v>400</v>
+      </c>
+      <c r="K35" s="90" t="s">
+        <v>62</v>
+      </c>
+      <c r="L35" s="91">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K36" s="90" t="s">
+        <v>1617</v>
+      </c>
+      <c r="L36" s="91"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K37" s="90" t="s">
+        <v>1614</v>
+      </c>
+      <c r="L37" s="91">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K17:L17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{625C978B-FB01-41AE-81FC-52945E433C67}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AM32"/>
@@ -49120,50 +51580,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" s="63" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="120" t="s">
         <v>1620</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
     </row>
     <row r="2" spans="1:39" s="63" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="107"/>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="107"/>
-      <c r="R2" s="107"/>
-      <c r="S2" s="107"/>
-      <c r="T2" s="107"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="120"/>
+      <c r="P2" s="120"/>
+      <c r="Q2" s="120"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="120"/>
+      <c r="T2" s="120"/>
     </row>
     <row r="3" spans="1:39" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q3" s="100" t="s">
